--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2022_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2022_T2_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="44">
   <si>
     <t/>
   </si>
@@ -45,48 +45,51 @@
     <t>N</t>
   </si>
   <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (1) </t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Mean/(SE)</t>
+  </si>
+  <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t>(0.000)</t>
+  </si>
+  <si>
+    <t>0.558</t>
+  </si>
+  <si>
+    <t>(0.070)</t>
+  </si>
+  <si>
+    <t>0.327</t>
+  </si>
+  <si>
+    <t>(0.066)</t>
+  </si>
+  <si>
+    <t>1.115</t>
+  </si>
+  <si>
+    <t>(0.190)</t>
+  </si>
+  <si>
+    <t>0.404</t>
+  </si>
+  <si>
+    <t>(0.092)</t>
+  </si>
+  <si>
     <t>58</t>
   </si>
   <si>
-    <t xml:space="preserve"> (1) </t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Mean/(SE)</t>
-  </si>
-  <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>(0.000)</t>
-  </si>
-  <si>
-    <t>0.500</t>
-  </si>
-  <si>
-    <t>(0.066)</t>
-  </si>
-  <si>
-    <t>0.293</t>
-  </si>
-  <si>
-    <t>(0.060)</t>
-  </si>
-  <si>
-    <t>1.000</t>
-  </si>
-  <si>
-    <t>(0.176)</t>
-  </si>
-  <si>
-    <t>0.362</t>
-  </si>
-  <si>
-    <t>(0.084)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> (2) </t>
   </si>
   <si>
@@ -120,7 +123,7 @@
     <t>.n</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -132,16 +135,16 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.379***</t>
-  </si>
-  <si>
-    <t>0.345***</t>
-  </si>
-  <si>
-    <t>3.397***</t>
-  </si>
-  <si>
-    <t>1.241***</t>
+    <t>0.322***</t>
+  </si>
+  <si>
+    <t>0.311***</t>
+  </si>
+  <si>
+    <t>3.281***</t>
+  </si>
+  <si>
+    <t>1.200***</t>
   </si>
 </sst>
 </file>
@@ -202,13 +205,13 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -225,13 +228,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -254,7 +257,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -268,16 +271,16 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -314,16 +317,16 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -340,7 +343,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -360,16 +363,16 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -386,7 +389,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -406,16 +409,16 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -452,16 +455,16 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -478,7 +481,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -498,16 +501,16 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
@@ -524,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
